--- a/artfynd/A 25672-2026 artfynd.xlsx
+++ b/artfynd/A 25672-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134433274</v>
+        <v>134433250</v>
       </c>
       <c r="B2" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391211</v>
+        <v>391161</v>
       </c>
       <c r="R2" t="n">
-        <v>6759354</v>
+        <v>6759097</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134433262</v>
+        <v>134433252</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391247</v>
+        <v>391218</v>
       </c>
       <c r="R3" t="n">
-        <v>6759288</v>
+        <v>6759132</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134433231</v>
+        <v>134433281</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391004</v>
+        <v>391043</v>
       </c>
       <c r="R4" t="n">
-        <v>6759335</v>
+        <v>6759349</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134433243</v>
+        <v>134433222</v>
       </c>
       <c r="B5" t="n">
-        <v>79985</v>
+        <v>81355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390997</v>
+        <v>390885</v>
       </c>
       <c r="R5" t="n">
-        <v>6759113</v>
+        <v>6759351</v>
       </c>
       <c r="S5" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>134433246</v>
       </c>
       <c r="B6" t="n">
-        <v>81348</v>
+        <v>81355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134433256</v>
+        <v>134433247</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>81355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>391280</v>
+        <v>391006</v>
       </c>
       <c r="R7" t="n">
-        <v>6759199</v>
+        <v>6759089</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134433251</v>
+        <v>134433279</v>
       </c>
       <c r="B8" t="n">
-        <v>79985</v>
+        <v>81355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>391189</v>
+        <v>391058</v>
       </c>
       <c r="R8" t="n">
-        <v>6759126</v>
+        <v>6759336</v>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,14 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134433265</v>
+        <v>134433216</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>391258</v>
+        <v>390752</v>
       </c>
       <c r="R9" t="n">
-        <v>6759311</v>
+        <v>6759426</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,14 +1531,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134433238</v>
+        <v>134433217</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>391001</v>
+        <v>390750</v>
       </c>
       <c r="R10" t="n">
-        <v>6759257</v>
+        <v>6759404</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134433259</v>
+        <v>134433218</v>
       </c>
       <c r="B11" t="n">
-        <v>79390</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>391286</v>
+        <v>390764</v>
       </c>
       <c r="R11" t="n">
-        <v>6759243</v>
+        <v>6759390</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,14 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134433253</v>
+        <v>134433234</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>391228</v>
+        <v>391022</v>
       </c>
       <c r="R12" t="n">
-        <v>6759145</v>
+        <v>6759298</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134433287</v>
+        <v>134433238</v>
       </c>
       <c r="B13" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>390958</v>
+        <v>391001</v>
       </c>
       <c r="R13" t="n">
-        <v>6759543</v>
+        <v>6759257</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,32 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134433237</v>
+        <v>134433240</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>390996</v>
+        <v>391047</v>
       </c>
       <c r="R14" t="n">
-        <v>6759273</v>
+        <v>6759194</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134433230</v>
+        <v>134433253</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>390988</v>
+        <v>391228</v>
       </c>
       <c r="R15" t="n">
-        <v>6759335</v>
+        <v>6759145</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:24</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134433244</v>
+        <v>134433255</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>390991</v>
+        <v>391271</v>
       </c>
       <c r="R16" t="n">
-        <v>6759107</v>
+        <v>6759178</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134433257</v>
+        <v>134433256</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>391272</v>
+        <v>391280</v>
       </c>
       <c r="R17" t="n">
-        <v>6759216</v>
+        <v>6759199</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134433261</v>
+        <v>134433262</v>
       </c>
       <c r="B18" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>391264</v>
+        <v>391247</v>
       </c>
       <c r="R18" t="n">
-        <v>6759265</v>
+        <v>6759288</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134433250</v>
+        <v>134433265</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>391161</v>
+        <v>391258</v>
       </c>
       <c r="R19" t="n">
-        <v>6759097</v>
+        <v>6759311</v>
       </c>
       <c r="S19" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134433228</v>
+        <v>134433272</v>
       </c>
       <c r="B20" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>390982</v>
+        <v>391236</v>
       </c>
       <c r="R20" t="n">
-        <v>6759343</v>
+        <v>6759371</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,14 +2708,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134433217</v>
+        <v>134433273</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>390750</v>
+        <v>391222</v>
       </c>
       <c r="R21" t="n">
-        <v>6759404</v>
+        <v>6759368</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134433239</v>
+        <v>134433276</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>391044</v>
+        <v>391187</v>
       </c>
       <c r="R22" t="n">
-        <v>6759194</v>
+        <v>6759341</v>
       </c>
       <c r="S22" t="n">
         <v>7</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134433248</v>
+        <v>134433233</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>391016</v>
+        <v>391007</v>
       </c>
       <c r="R23" t="n">
-        <v>6759098</v>
+        <v>6759336</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,32 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134433224</v>
+        <v>134433259</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>390948</v>
+        <v>391286</v>
       </c>
       <c r="R24" t="n">
-        <v>6759337</v>
+        <v>6759243</v>
       </c>
       <c r="S24" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134433260</v>
+        <v>134433264</v>
       </c>
       <c r="B25" t="n">
-        <v>79985</v>
+        <v>79397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>391288</v>
+        <v>391258</v>
       </c>
       <c r="R25" t="n">
-        <v>6759243</v>
+        <v>6759299</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134433272</v>
+        <v>134433225</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>78776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>391236</v>
+        <v>390950</v>
       </c>
       <c r="R26" t="n">
-        <v>6759371</v>
+        <v>6759349</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134433280</v>
+        <v>134433213</v>
       </c>
       <c r="B27" t="n">
-        <v>79985</v>
+        <v>83358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>391043</v>
+        <v>390744</v>
       </c>
       <c r="R27" t="n">
-        <v>6759351</v>
+        <v>6759501</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134433271</v>
+        <v>134433220</v>
       </c>
       <c r="B28" t="n">
-        <v>79956</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>391263</v>
+        <v>390776</v>
       </c>
       <c r="R28" t="n">
-        <v>6759338</v>
+        <v>6759394</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134433252</v>
+        <v>134433226</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>391218</v>
+        <v>390954</v>
       </c>
       <c r="R29" t="n">
-        <v>6759132</v>
+        <v>6759344</v>
       </c>
       <c r="S29" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134433225</v>
+        <v>134433228</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>390950</v>
+        <v>390982</v>
       </c>
       <c r="R30" t="n">
-        <v>6759349</v>
+        <v>6759343</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134433247</v>
+        <v>134433232</v>
       </c>
       <c r="B31" t="n">
-        <v>81348</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>391006</v>
+        <v>391007</v>
       </c>
       <c r="R31" t="n">
-        <v>6759089</v>
+        <v>6759338</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134433278</v>
+        <v>134433235</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>391090</v>
+        <v>391003</v>
       </c>
       <c r="R32" t="n">
-        <v>6759325</v>
+        <v>6759276</v>
       </c>
       <c r="S32" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134433279</v>
+        <v>134433236</v>
       </c>
       <c r="B33" t="n">
-        <v>81348</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4003,21 +4003,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4027,13 +4027,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>391058</v>
+        <v>390997</v>
       </c>
       <c r="R33" t="n">
-        <v>6759336</v>
+        <v>6759287</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134433284</v>
+        <v>134433237</v>
       </c>
       <c r="B34" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>391022</v>
+        <v>390996</v>
       </c>
       <c r="R34" t="n">
-        <v>6759372</v>
+        <v>6759273</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134433258</v>
+        <v>134433241</v>
       </c>
       <c r="B35" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>391274</v>
+        <v>391022</v>
       </c>
       <c r="R35" t="n">
-        <v>6759226</v>
+        <v>6759139</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,10 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134433234</v>
+        <v>134433243</v>
       </c>
       <c r="B36" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>391022</v>
+        <v>390997</v>
       </c>
       <c r="R36" t="n">
-        <v>6759298</v>
+        <v>6759113</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134433267</v>
+        <v>134433251</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>391266</v>
+        <v>391189</v>
       </c>
       <c r="R37" t="n">
-        <v>6759335</v>
+        <v>6759126</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134433232</v>
+        <v>134433258</v>
       </c>
       <c r="B38" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>391007</v>
+        <v>391274</v>
       </c>
       <c r="R38" t="n">
-        <v>6759338</v>
+        <v>6759226</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134433281</v>
+        <v>134433260</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>391043</v>
+        <v>391288</v>
       </c>
       <c r="R39" t="n">
-        <v>6759349</v>
+        <v>6759243</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134433241</v>
+        <v>134433261</v>
       </c>
       <c r="B40" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4776,13 +4776,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>391022</v>
+        <v>391264</v>
       </c>
       <c r="R40" t="n">
-        <v>6759139</v>
+        <v>6759265</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134433275</v>
+        <v>134433263</v>
       </c>
       <c r="B41" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4883,13 +4883,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>391207</v>
+        <v>391251</v>
       </c>
       <c r="R41" t="n">
-        <v>6759358</v>
+        <v>6759293</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,10 +4955,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134433229</v>
+        <v>134433266</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>390985</v>
+        <v>391264</v>
       </c>
       <c r="R42" t="n">
-        <v>6759338</v>
+        <v>6759328</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134433283</v>
+        <v>134433274</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5097,13 +5097,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>391024</v>
+        <v>391211</v>
       </c>
       <c r="R43" t="n">
-        <v>6759369</v>
+        <v>6759354</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134433263</v>
+        <v>134433275</v>
       </c>
       <c r="B44" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>391251</v>
+        <v>391207</v>
       </c>
       <c r="R44" t="n">
-        <v>6759293</v>
+        <v>6759358</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134433273</v>
+        <v>134433277</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,13 +5311,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>391222</v>
+        <v>391126</v>
       </c>
       <c r="R45" t="n">
-        <v>6759368</v>
+        <v>6759327</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134433226</v>
+        <v>134433280</v>
       </c>
       <c r="B46" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5418,13 +5418,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>390954</v>
+        <v>391043</v>
       </c>
       <c r="R46" t="n">
-        <v>6759344</v>
+        <v>6759351</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134433266</v>
+        <v>134433284</v>
       </c>
       <c r="B47" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>391264</v>
+        <v>391022</v>
       </c>
       <c r="R47" t="n">
-        <v>6759328</v>
+        <v>6759372</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5597,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134433233</v>
+        <v>134433286</v>
       </c>
       <c r="B48" t="n">
-        <v>79390</v>
+        <v>79992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>391007</v>
+        <v>391027</v>
       </c>
       <c r="R48" t="n">
-        <v>6759336</v>
+        <v>6759434</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134433236</v>
+        <v>134433287</v>
       </c>
       <c r="B49" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5739,13 +5739,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>390997</v>
+        <v>390958</v>
       </c>
       <c r="R49" t="n">
-        <v>6759287</v>
+        <v>6759543</v>
       </c>
       <c r="S49" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,10 +5811,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134433276</v>
+        <v>134433219</v>
       </c>
       <c r="B50" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,21 +5822,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,13 +5846,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>391187</v>
+        <v>390775</v>
       </c>
       <c r="R50" t="n">
-        <v>6759341</v>
+        <v>6759390</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,10 +5918,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134433216</v>
+        <v>134433223</v>
       </c>
       <c r="B51" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,21 +5929,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>390752</v>
+        <v>390926</v>
       </c>
       <c r="R51" t="n">
-        <v>6759426</v>
+        <v>6759352</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134433254</v>
+        <v>134433224</v>
       </c>
       <c r="B52" t="n">
-        <v>79956</v>
+        <v>79131</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,13 +6060,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>391253</v>
+        <v>390948</v>
       </c>
       <c r="R52" t="n">
-        <v>6759164</v>
+        <v>6759337</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134433277</v>
+        <v>134433227</v>
       </c>
       <c r="B53" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,13 +6167,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>391126</v>
+        <v>390991</v>
       </c>
       <c r="R53" t="n">
-        <v>6759327</v>
+        <v>6759342</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134433286</v>
+        <v>134433229</v>
       </c>
       <c r="B54" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>391027</v>
+        <v>390985</v>
       </c>
       <c r="R54" t="n">
-        <v>6759434</v>
+        <v>6759338</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134433222</v>
+        <v>134433230</v>
       </c>
       <c r="B55" t="n">
-        <v>81348</v>
+        <v>79131</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>390885</v>
+        <v>390988</v>
       </c>
       <c r="R55" t="n">
-        <v>6759351</v>
+        <v>6759335</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6453,10 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134433285</v>
+        <v>134433231</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>391026</v>
+        <v>391004</v>
       </c>
       <c r="R56" t="n">
-        <v>6759399</v>
+        <v>6759335</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6560,10 +6560,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134433240</v>
+        <v>134433239</v>
       </c>
       <c r="B57" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6571,21 +6571,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6595,13 +6595,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>391047</v>
+        <v>391044</v>
       </c>
       <c r="R57" t="n">
         <v>6759194</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134433282</v>
+        <v>134433242</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6702,13 +6702,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>391039</v>
+        <v>390991</v>
       </c>
       <c r="R58" t="n">
-        <v>6759352</v>
+        <v>6759120</v>
       </c>
       <c r="S58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6774,10 +6774,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134433227</v>
+        <v>134433244</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         <v>390991</v>
       </c>
       <c r="R59" t="n">
-        <v>6759342</v>
+        <v>6759107</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6881,10 +6881,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134433235</v>
+        <v>134433248</v>
       </c>
       <c r="B60" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6916,13 +6916,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>391003</v>
+        <v>391016</v>
       </c>
       <c r="R60" t="n">
-        <v>6759276</v>
+        <v>6759098</v>
       </c>
       <c r="S60" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6988,32 +6988,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134433264</v>
+        <v>134433257</v>
       </c>
       <c r="B61" t="n">
-        <v>79390</v>
+        <v>79131</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>391258</v>
+        <v>391272</v>
       </c>
       <c r="R61" t="n">
-        <v>6759299</v>
+        <v>6759216</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134433223</v>
+        <v>134433267</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7130,13 +7130,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>390926</v>
+        <v>391266</v>
       </c>
       <c r="R62" t="n">
-        <v>6759352</v>
+        <v>6759335</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7202,10 +7202,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134433242</v>
+        <v>134433278</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7237,13 +7237,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>390991</v>
+        <v>391090</v>
       </c>
       <c r="R63" t="n">
-        <v>6759120</v>
+        <v>6759325</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7306,6 +7306,541 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134433282</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>391039</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6759352</v>
+      </c>
+      <c r="S64" t="n">
+        <v>14</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134433283</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>391024</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6759369</v>
+      </c>
+      <c r="S65" t="n">
+        <v>6</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134433285</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>391026</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6759399</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134433254</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>391253</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6759164</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134433271</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Dalheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>391263</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6759338</v>
+      </c>
+      <c r="S68" t="n">
+        <v>12</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25672-2026 artfynd.xlsx
+++ b/artfynd/A 25672-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433246</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433247</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433279</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433216</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433217</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433218</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433234</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433238</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433253</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433255</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433256</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433262</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433265</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433272</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433276</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433233</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433259</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433264</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433225</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433213</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433220</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433226</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433228</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433232</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433235</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433236</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433237</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433241</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433243</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433251</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433258</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433260</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433261</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433263</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433266</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433274</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433275</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433277</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433280</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433284</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433286</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433287</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433219</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433223</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433224</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433227</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433229</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433230</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433231</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433239</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433242</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433244</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433248</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433257</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433267</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433278</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433282</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7520,6 +7840,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433283</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433285</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433254</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,8 +8176,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>